--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C1104D-1457-441F-9DBD-D811C9EADCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4338DFAD-E5C7-4D21-A32E-0410606B52FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15435" yWindow="-15000" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -155,6 +155,33 @@
     <t>ダメージ量</t>
     <rPh sb="4" eb="5">
       <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP10回復</t>
+    <rPh sb="4" eb="6">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度50回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度100回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -516,11 +543,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.375" bestFit="1" customWidth="1"/>
@@ -586,23 +613,25 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C3" s="2">
         <f>VLOOKUP(D3,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="str">
         <f>VLOOKUP(D3,reference!A:D,3,FALSE)</f>
-        <v>威力%</v>
+        <v>回復量</v>
       </c>
       <c r="H3" s="2" t="str">
         <f>VLOOKUP(D3,reference!A:D,4,FALSE)</f>
@@ -613,23 +642,25 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C4" s="2">
         <f>VLOOKUP(D4,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="str">
         <f>VLOOKUP(D4,reference!A:D,3,FALSE)</f>
-        <v>威力%</v>
+        <v>回復量</v>
       </c>
       <c r="H4" s="2" t="str">
         <f>VLOOKUP(D4,reference!A:D,4,FALSE)</f>
@@ -640,26 +671,82 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C5" s="2">
         <f>VLOOKUP(D5,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="str">
         <f>VLOOKUP(D5,reference!A:D,3,FALSE)</f>
-        <v>威力%</v>
+        <v>回復量</v>
       </c>
       <c r="H5" s="2" t="str">
         <f>VLOOKUP(D5,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2">
+        <f>VLOOKUP(D6,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f>VLOOKUP(D6,reference!A:D,3,FALSE)</f>
+        <v>ダメージ量</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f>VLOOKUP(D6,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2">
+        <f>VLOOKUP(D7,reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <f>VLOOKUP(D7,reference!A:D,3,FALSE)</f>
+        <v>威力%</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <f>VLOOKUP(D7,reference!A:D,4,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
@@ -674,7 +761,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D5</xm:sqref>
+          <xm:sqref>D2:D7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4338DFAD-E5C7-4D21-A32E-0410606B52FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D910672-0502-4EE6-A16D-CA2444678CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8010" yWindow="-14130" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="22">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -183,6 +183,14 @@
     <rPh sb="6" eb="8">
       <t>カイフク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31ダメージ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -700,7 +708,9 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" s="2">
         <f>VLOOKUP(D6,reference!A:B,2,FALSE)</f>
         <v>3</v>
@@ -709,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -727,23 +737,25 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C7" s="2">
         <f>VLOOKUP(D7,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="str">
         <f>VLOOKUP(D7,reference!A:D,3,FALSE)</f>
-        <v>威力%</v>
+        <v>ダメージ量</v>
       </c>
       <c r="H7" s="2" t="str">
         <f>VLOOKUP(D7,reference!A:D,4,FALSE)</f>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D910672-0502-4EE6-A16D-CA2444678CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC004259-5A1F-4001-88EC-C308674F2A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8010" yWindow="-14130" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="-14610" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -191,6 +191,10 @@
   </si>
   <si>
     <t>31ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5ダメージ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -551,11 +555,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="8.375" bestFit="1" customWidth="1"/>
@@ -759,6 +763,93 @@
       </c>
       <c r="H7" s="2" t="str">
         <f>VLOOKUP(D7,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <f>VLOOKUP(D8,reference!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f>VLOOKUP(D8,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <f>VLOOKUP(D8,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2">
+        <f>VLOOKUP(D9,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <f>VLOOKUP(D9,reference!A:D,3,FALSE)</f>
+        <v>ダメージ量</v>
+      </c>
+      <c r="H9" s="2" t="str">
+        <f>VLOOKUP(D9,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2">
+        <f>VLOOKUP(D10,reference!A:B,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f>VLOOKUP(D10,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <f>VLOOKUP(D10,reference!A:D,4,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
@@ -773,7 +864,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D7</xm:sqref>
+          <xm:sqref>D2:D10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC004259-5A1F-4001-88EC-C308674F2A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE3DF1D-2999-4896-AC9A-5DC44A147E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="-14610" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="-15000" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -195,6 +195,51 @@
   </si>
   <si>
     <t>5ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場所替え</t>
+    <rPh sb="0" eb="3">
+      <t>バショガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>25ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吹き飛ばし</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マス数</t>
+    <rPh sb="2" eb="3">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープ</t>
+  </si>
+  <si>
+    <t>10マス吹き飛ばし</t>
+    <rPh sb="4" eb="5">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ト</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -555,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -853,6 +898,122 @@
         <v>未使用</v>
       </c>
     </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2">
+        <f>VLOOKUP(D11,reference!A:B,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="str">
+        <f>VLOOKUP(D11,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H11" s="2" t="str">
+        <f>VLOOKUP(D11,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2">
+        <f>VLOOKUP(D12,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f>VLOOKUP(D12,reference!A:D,3,FALSE)</f>
+        <v>ダメージ量</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <f>VLOOKUP(D12,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2">
+        <f>VLOOKUP(D13,reference!A:B,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="str">
+        <f>VLOOKUP(D13,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H13" s="2" t="str">
+        <f>VLOOKUP(D13,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2">
+        <f>VLOOKUP(D14,reference!A:B,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="2">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="str">
+        <f>VLOOKUP(D14,reference!A:D,3,FALSE)</f>
+        <v>マス数</v>
+      </c>
+      <c r="H14" s="2" t="str">
+        <f>VLOOKUP(D14,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -864,7 +1025,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D10</xm:sqref>
+          <xm:sqref>D2:D14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -874,12 +1035,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7B5D92-8AB0-4E58-AB32-5914247D4A74}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -980,6 +1142,34 @@
         <v>14</v>
       </c>
     </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE3DF1D-2999-4896-AC9A-5DC44A147E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EC8F5D-3EEF-4426-A423-932B4F028E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="-15000" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="-13905" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -239,6 +239,26 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>罠を可視化</t>
+    <rPh sb="0" eb="1">
+      <t>ワナ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆発効果</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -600,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -1014,6 +1034,33 @@
         <v>未使用</v>
       </c>
     </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2">
+        <f>VLOOKUP(D15,reference!A:B,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="str">
+        <f>VLOOKUP(D15,reference!A:D,3,FALSE)</f>
+        <v>未使用</v>
+      </c>
+      <c r="H15" s="2" t="str">
+        <f>VLOOKUP(D15,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1025,7 +1072,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D14</xm:sqref>
+          <xm:sqref>D2:D15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1035,11 +1082,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7B5D92-8AB0-4E58-AB32-5914247D4A74}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1170,8 +1217,37 @@
         <v>14</v>
       </c>
     </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EC8F5D-3EEF-4426-A423-932B4F028E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D14825-4A8A-4CE3-B03A-617FBDFDF8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="-13905" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="945" yWindow="-13800" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="36">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -259,6 +259,34 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>割合</t>
+    <rPh sb="0" eb="2">
+      <t>ワリアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーは死亡しない</t>
+    <rPh sb="6" eb="8">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50%爆発ダメージ</t>
+    <rPh sb="3" eb="5">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>100%爆発ダメージ</t>
+    <rPh sb="4" eb="6">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -620,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -1061,6 +1089,64 @@
         <v>未使用</v>
       </c>
     </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2">
+        <f>VLOOKUP(D16,reference!A:B,2,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="str">
+        <f>VLOOKUP(D16,reference!A:D,3,FALSE)</f>
+        <v>割合</v>
+      </c>
+      <c r="H16" s="2" t="str">
+        <f>VLOOKUP(D16,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <f>VLOOKUP(D17,reference!A:B,2,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="str">
+        <f>VLOOKUP(D17,reference!A:D,3,FALSE)</f>
+        <v>割合</v>
+      </c>
+      <c r="H17" s="2" t="str">
+        <f>VLOOKUP(D17,reference!A:D,4,FALSE)</f>
+        <v>未使用</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1072,7 +1158,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D15</xm:sqref>
+          <xm:sqref>D2:D17</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1082,16 +1168,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7B5D92-8AB0-4E58-AB32-5914247D4A74}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1105,7 +1192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1119,7 +1206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1133,7 +1220,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1147,7 +1234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1161,7 +1248,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1175,7 +1262,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1189,7 +1276,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1203,7 +1290,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1217,7 +1304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1231,7 +1318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -1239,10 +1326,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
